--- a/ПУ3/Модуль 1/Прил_2_ОЗ_КОД 09.02.07-2-2026-М1/import/4Пункты выдачи_import.xlsx
+++ b/ПУ3/Модуль 1/Прил_2_ОЗ_КОД 09.02.07-2-2026-М1/import/4Пункты выдачи_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\МДК.04.02(Кретинин)\demka4\ПУ3\Модуль 1\Прил_2_ОЗ_КОД 09.02.07-2-2026-М1\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1BA7FA-8810-4BE4-B697-1D30E7DD302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D315277D-E546-4FC6-A0E6-FA8C8D2A020F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Index</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>CityId</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
 </sst>
 </file>
@@ -500,530 +503,640 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
         <v>630100</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
         <v>630101</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
         <v>630102</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
         <v>630103</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
         <v>630104</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
         <v>630105</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
         <v>630106</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>7</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
         <v>630107</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
         <v>630108</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
         <v>630109</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
         <v>630110</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
         <v>630111</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
         <v>630112</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>13</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
         <v>630113</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
         <v>630114</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
         <v>630115</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
         <v>630116</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
         <v>17</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
         <v>630117</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
         <v>18</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
         <v>630118</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
         <v>19</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
         <v>630119</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
         <v>630120</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
         <v>21</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
         <v>630121</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
         <v>22</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
         <v>630122</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
         <v>23</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
         <v>630123</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
         <v>24</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
         <v>630124</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>25</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
         <v>630125</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
         <v>26</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
         <v>630126</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
         <v>27</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
         <v>630127</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
         <v>28</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
         <v>630128</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
         <v>29</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
         <v>630129</v>
       </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
         <v>30</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
         <v>630130</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
         <v>31</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
         <v>630131</v>
       </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
         <v>32</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
         <v>630132</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
         <v>33</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
         <v>630133</v>
       </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
         <v>34</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
         <v>630134</v>
       </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
         <v>35</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
         <v>630135</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
         <v>36</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>80</v>
       </c>
     </row>
